--- a/artfynd/A 10492-2026 artfynd.xlsx
+++ b/artfynd/A 10492-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94111281</v>
+        <v>94110886</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ockelbo, Gstr</t>
+          <t>Ivantjärn, Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583461.251467563</v>
+        <v>583447</v>
       </c>
       <c r="R2" t="n">
-        <v>6741574.211621098</v>
+        <v>6741610</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +758,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På tallhögstubbe i "slänt"</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,52 +791,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94113941</v>
+        <v>94111391</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ockelbo, Gstr</t>
+          <t>Ivantjärn, Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582955.5337369272</v>
+        <v>583399</v>
       </c>
       <c r="R3" t="n">
-        <v>6741322.181056131</v>
+        <v>6741581</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt i denna del</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94111334</v>
+        <v>94111384</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,35 +910,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ockelbo, Gstr</t>
+          <t>Ivantjärn, Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583415.1994258572</v>
+        <v>583401</v>
       </c>
       <c r="R4" t="n">
-        <v>6741598.526768991</v>
+        <v>6741578</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +970,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +980,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På lågan även rosenticka</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,12 +1015,7 @@
         <v>94113043</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583346.8899868279</v>
+        <v>583347</v>
       </c>
       <c r="R5" t="n">
-        <v>6741382.078167678</v>
+        <v>6741382</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1133,15 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94113401</v>
+        <v>94113498</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583159.927303476</v>
+        <v>583149</v>
       </c>
       <c r="R6" t="n">
-        <v>6741366.488505244</v>
+        <v>6741379</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1209,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1201,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fjolårsfruktkropppar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,37 +1233,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94113114</v>
+        <v>94111327</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583303.8162174285</v>
+        <v>583418</v>
       </c>
       <c r="R7" t="n">
-        <v>6741362.517055164</v>
+        <v>6741588</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,52 +1341,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94112384</v>
+        <v>94111334</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583325.2461832812</v>
+        <v>583415</v>
       </c>
       <c r="R8" t="n">
-        <v>6741345.437386503</v>
+        <v>6741599</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1412,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1422,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,52 +1449,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>94113901</v>
+        <v>94113114</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582940.8684381255</v>
+        <v>583304</v>
       </c>
       <c r="R9" t="n">
-        <v>6741321.84044958</v>
+        <v>6741363</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1550,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,51 +1557,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94111384</v>
+        <v>94110961</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ivantjärn, Ockelbo, Gstr</t>
+          <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583401.4799561431</v>
+        <v>583426</v>
       </c>
       <c r="R10" t="n">
-        <v>6741578.674702071</v>
+        <v>6741620</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1663,7 +1628,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1673,12 +1638,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På lågan även rosenticka</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,19 +1665,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>94112220</v>
+        <v>94111281</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1746,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583195.4988414517</v>
+        <v>583461</v>
       </c>
       <c r="R11" t="n">
-        <v>6741309.206501824</v>
+        <v>6741574</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1781,7 +1736,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1746,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,19 +1773,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>94112886</v>
+        <v>94112220</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1855,14 +1805,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ivantjärn, Ockelbo, Gstr</t>
+          <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583393.932150191</v>
+        <v>583195</v>
       </c>
       <c r="R12" t="n">
-        <v>6741378.293133938</v>
+        <v>6741309</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1894,7 +1844,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,7 +1854,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,19 +1881,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>94110961</v>
+        <v>94112398</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1968,14 +1913,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ockelbo, Gstr</t>
+          <t>Ivantjärn, Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583426.9293252535</v>
+        <v>583340</v>
       </c>
       <c r="R13" t="n">
-        <v>6741619.797166324</v>
+        <v>6741361</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +1952,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +1962,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,15 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>94111472</v>
+        <v>94112767</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,36 +2000,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ivantjärn, Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583336.5718021877</v>
+        <v>583475</v>
       </c>
       <c r="R14" t="n">
-        <v>6741551.768137568</v>
+        <v>6741364</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2121,7 +2060,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2070,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,15 +2097,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>94112613</v>
+        <v>94112886</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2174,36 +2108,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ivantjärn, Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583373.5968894886</v>
+        <v>583394</v>
       </c>
       <c r="R15" t="n">
-        <v>6741327.52112582</v>
+        <v>6741378</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2235,7 +2168,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2245,7 +2178,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,15 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>94112862</v>
+        <v>94112984</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,36 +2216,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ivantjärn, Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583410.9958160017</v>
+        <v>583342</v>
       </c>
       <c r="R16" t="n">
-        <v>6741380.644898484</v>
+        <v>6741379</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2349,7 +2276,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2286,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,19 +2313,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>94112984</v>
+        <v>94113401</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2423,14 +2345,14 @@
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ivantjärn, Ockelbo, Gstr</t>
+          <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583342.069967587</v>
+        <v>583160</v>
       </c>
       <c r="R17" t="n">
-        <v>6741379.035772525</v>
+        <v>6741367</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2462,7 +2384,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2472,7 +2394,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,15 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>94112746</v>
+        <v>94113589</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2515,36 +2432,35 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ivantjärn, Ockelbo, Gstr</t>
+          <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583472.9997653228</v>
+        <v>583115</v>
       </c>
       <c r="R18" t="n">
-        <v>6741364.514026743</v>
+        <v>6741361</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2576,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2586,7 +2502,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,51 +2529,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>94111327</v>
+        <v>97604827</v>
       </c>
       <c r="B19" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ockelbo, Gstr</t>
+          <t>Ivantjärn, V Mursveden, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583418.3830586623</v>
+        <v>583044</v>
       </c>
       <c r="R19" t="n">
-        <v>6741587.858751566</v>
+        <v>6741368</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2684,22 +2594,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:31</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-06-07</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:31</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2714,63 +2614,63 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>94112398</v>
+        <v>94111472</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Ivantjärn, Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583340.0471788888</v>
+        <v>583337</v>
       </c>
       <c r="R20" t="n">
-        <v>6741360.920730007</v>
+        <v>6741551</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2802,7 +2702,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2712,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2839,51 +2739,47 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>94113589</v>
+        <v>94111975</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ockelbo, Gstr</t>
+          <t>Ivantjärn, Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583115.0791969545</v>
+        <v>583386</v>
       </c>
       <c r="R21" t="n">
-        <v>6741360.072986677</v>
+        <v>6741709</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2915,7 +2811,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2925,7 +2821,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2952,51 +2848,47 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>94111391</v>
+        <v>94112384</v>
       </c>
       <c r="B22" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ivantjärn, Ockelbo, Gstr</t>
+          <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583399.4563378713</v>
+        <v>583325</v>
       </c>
       <c r="R22" t="n">
-        <v>6741581.557193036</v>
+        <v>6741345</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3028,7 +2920,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3038,7 +2930,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3065,15 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>94113522</v>
+        <v>94112613</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3103,14 +2990,14 @@
       <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ockelbo, Gstr</t>
+          <t>Ivantjärn, Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583148.8660827588</v>
+        <v>583373</v>
       </c>
       <c r="R23" t="n">
-        <v>6741379.415552719</v>
+        <v>6741328</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3142,7 +3029,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3152,7 +3039,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3179,51 +3066,47 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>94112767</v>
+        <v>94112746</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ivantjärn, Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583474.9779321084</v>
+        <v>583473</v>
       </c>
       <c r="R24" t="n">
-        <v>6741363.583618714</v>
+        <v>6741364</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3255,7 +3138,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3265,7 +3148,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3292,51 +3175,47 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>94113498</v>
+        <v>94112862</v>
       </c>
       <c r="B25" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ockelbo, Gstr</t>
+          <t>Ivantjärn, Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583148.8660827588</v>
+        <v>583411</v>
       </c>
       <c r="R25" t="n">
-        <v>6741379.415552719</v>
+        <v>6741381</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3368,7 +3247,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3378,12 +3257,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:58</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Fjolårsfruktkropppar</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3410,56 +3284,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>94110886</v>
+        <v>94113522</v>
       </c>
       <c r="B26" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>306</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ivantjärn, Ockelbo, Gstr</t>
+          <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583447.2097283935</v>
+        <v>583149</v>
       </c>
       <c r="R26" t="n">
-        <v>6741610.016977942</v>
+        <v>6741379</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3488,7 +3356,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3498,12 +3366,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På tallhögstubbe i "slänt"</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3512,7 +3375,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3531,15 +3393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>97604694</v>
+        <v>94113901</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3565,16 +3422,18 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ivantjärn, V Mursveden, Gstr</t>
+          <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583066.6515819011</v>
+        <v>582940</v>
       </c>
       <c r="R27" t="n">
-        <v>6741402.4064581</v>
+        <v>6741322</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3601,22 +3460,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3631,66 +3490,59 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
-        </is>
-      </c>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97604827</v>
+        <v>94113918</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ivantjärn, V Mursveden, Gstr</t>
+          <t>Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583043.9706692918</v>
+        <v>582956</v>
       </c>
       <c r="R28" t="n">
-        <v>6741368.185203989</v>
+        <v>6741322</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3717,22 +3569,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3747,31 +3599,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
-        </is>
-      </c>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>97604828</v>
+        <v>97604694</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3803,10 +3646,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583073.6521382495</v>
+        <v>583066</v>
       </c>
       <c r="R29" t="n">
-        <v>6741332.739771069</v>
+        <v>6741403</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3833,22 +3676,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3872,6 +3705,208 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>97604828</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ivantjärn, V Mursveden, Gstr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>583073</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6741332</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-05-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-05-19</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Gävleborg funktionsindelning</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>97604693</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ivantjärn, V Mursveden, Gstr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>583171</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6741375</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
         <is>
           <t>Länsstyrelsen Gävleborg funktionsindelning</t>
         </is>
